--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/IOWA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/IOWA_2017.xlsx
@@ -481,7 +481,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="8">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="32">
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="34">
@@ -1435,7 +1435,7 @@
         <v>3</v>
       </c>
       <c r="D60">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="61">
@@ -1633,7 +1633,7 @@
         <v>3</v>
       </c>
       <c r="D71">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="72">
@@ -1669,7 +1669,7 @@
         <v>3</v>
       </c>
       <c r="D73">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="74">
@@ -2065,7 +2065,7 @@
         <v>3</v>
       </c>
       <c r="D95">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="96">
@@ -2227,7 +2227,7 @@
         <v>3</v>
       </c>
       <c r="D104">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="105">
@@ -2677,7 +2677,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="130">
@@ -3001,7 +3001,7 @@
         <v>3</v>
       </c>
       <c r="D147">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="148">
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="D157">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="158">
@@ -3253,7 +3253,7 @@
         <v>3</v>
       </c>
       <c r="D161">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="162">
@@ -3343,7 +3343,7 @@
         <v>3</v>
       </c>
       <c r="D166">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="167">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C169">
@@ -3433,7 +3433,7 @@
         <v>3</v>
       </c>
       <c r="D171">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="172">
@@ -3541,7 +3541,7 @@
         <v>3</v>
       </c>
       <c r="D177">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="178">
@@ -3685,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="D185">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="186">
@@ -3703,7 +3703,7 @@
         <v>3</v>
       </c>
       <c r="D186">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="187">
@@ -3757,7 +3757,7 @@
         <v>3</v>
       </c>
       <c r="D189">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="190">
@@ -4117,7 +4117,7 @@
         <v>3</v>
       </c>
       <c r="D209">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="210">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D211">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="212">
@@ -4243,7 +4243,7 @@
         <v>3</v>
       </c>
       <c r="D216">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="217">
@@ -4261,7 +4261,7 @@
         <v>3</v>
       </c>
       <c r="D217">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="218">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D218">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="219">
@@ -4297,7 +4297,7 @@
         <v>3</v>
       </c>
       <c r="D219">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="220">
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="D261">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="262">
@@ -5881,7 +5881,7 @@
         <v>3</v>
       </c>
       <c r="D307">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="308">
@@ -5989,7 +5989,7 @@
         <v>3</v>
       </c>
       <c r="D313">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="314">
@@ -6061,7 +6061,7 @@
         <v>3</v>
       </c>
       <c r="D317">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="318">
@@ -6187,7 +6187,7 @@
         <v>3</v>
       </c>
       <c r="D324">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="325">
@@ -6277,7 +6277,7 @@
         <v>3</v>
       </c>
       <c r="D329">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="330">
@@ -6673,7 +6673,7 @@
         <v>3</v>
       </c>
       <c r="D351">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="352">
@@ -6709,7 +6709,7 @@
         <v>3</v>
       </c>
       <c r="D353">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="354">
@@ -6871,7 +6871,7 @@
         <v>3</v>
       </c>
       <c r="D362">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="363">
@@ -7177,7 +7177,7 @@
         <v>3</v>
       </c>
       <c r="D379">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="380">
@@ -7357,7 +7357,7 @@
         <v>3</v>
       </c>
       <c r="D389">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="390">
@@ -7411,7 +7411,7 @@
         <v>3</v>
       </c>
       <c r="D392">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="393">
@@ -7699,7 +7699,7 @@
         <v>3</v>
       </c>
       <c r="D408">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="409">
@@ -7897,7 +7897,7 @@
         <v>3</v>
       </c>
       <c r="D419">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="420">
@@ -8041,7 +8041,7 @@
         <v>3</v>
       </c>
       <c r="D427">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="428">
@@ -8149,7 +8149,7 @@
         <v>3</v>
       </c>
       <c r="D433">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="434">
@@ -8185,7 +8185,7 @@
         <v>3</v>
       </c>
       <c r="D435">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="436">
@@ -8311,7 +8311,7 @@
         <v>3</v>
       </c>
       <c r="D442">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="443">
@@ -8455,7 +8455,7 @@
         <v>3</v>
       </c>
       <c r="D450">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="451">
@@ -8635,7 +8635,7 @@
         <v>3</v>
       </c>
       <c r="D460">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="461">
@@ -8851,7 +8851,7 @@
         <v>3</v>
       </c>
       <c r="D472">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="473">
@@ -8887,7 +8887,7 @@
         <v>3</v>
       </c>
       <c r="D474">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="475">
@@ -9211,7 +9211,7 @@
         <v>3</v>
       </c>
       <c r="D492">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="493">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C503">
@@ -9967,7 +9967,7 @@
         <v>3</v>
       </c>
       <c r="D534">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="535">
@@ -10147,7 +10147,7 @@
         <v>3</v>
       </c>
       <c r="D544">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="545">
@@ -10345,7 +10345,7 @@
         <v>3</v>
       </c>
       <c r="D555">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="556">
@@ -10507,7 +10507,7 @@
         <v>3</v>
       </c>
       <c r="D564">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="565">
@@ -10687,7 +10687,7 @@
         <v>3</v>
       </c>
       <c r="D574">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="575">
@@ -10849,7 +10849,7 @@
         <v>3</v>
       </c>
       <c r="D583">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="584">
@@ -10867,7 +10867,7 @@
         <v>3</v>
       </c>
       <c r="D584">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="585">
@@ -10903,7 +10903,7 @@
         <v>3</v>
       </c>
       <c r="D586">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="587">
@@ -10921,7 +10921,7 @@
         <v>3</v>
       </c>
       <c r="D587">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="588">
@@ -10939,7 +10939,7 @@
         <v>3</v>
       </c>
       <c r="D588">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="589">
@@ -11713,7 +11713,7 @@
         <v>3</v>
       </c>
       <c r="D631">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="632">
@@ -11875,7 +11875,7 @@
         <v>3</v>
       </c>
       <c r="D640">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="641">
@@ -12127,7 +12127,7 @@
         <v>3</v>
       </c>
       <c r="D654">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="655">
@@ -12469,7 +12469,7 @@
         <v>3</v>
       </c>
       <c r="D673">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="674">
@@ -12505,7 +12505,7 @@
         <v>3</v>
       </c>
       <c r="D675">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="676">
@@ -12919,7 +12919,7 @@
         <v>3</v>
       </c>
       <c r="D698">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="699">
@@ -13099,7 +13099,7 @@
         <v>3</v>
       </c>
       <c r="D708">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="709">
@@ -13225,7 +13225,7 @@
         <v>3</v>
       </c>
       <c r="D715">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="716">
@@ -13711,7 +13711,7 @@
         <v>3</v>
       </c>
       <c r="D742">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="743">
@@ -13837,7 +13837,7 @@
         <v>3</v>
       </c>
       <c r="D749">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="750">
@@ -13927,7 +13927,7 @@
         <v>3</v>
       </c>
       <c r="D754">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="755">
@@ -13963,7 +13963,7 @@
         <v>3</v>
       </c>
       <c r="D756">
-        <v>0.0009380863039399625</v>
+        <v>0.0009380863039399624</v>
       </c>
     </row>
     <row r="757">
